--- a/rivr-tech-business-plan/RIVR_Tech_Five_Year_Financial_Model_2027-2031.xlsx
+++ b/rivr-tech-business-plan/RIVR_Tech_Five_Year_Financial_Model_2027-2031.xlsx
@@ -4948,7 +4948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J14"/>
+  <dimension ref="B1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="2" max="2"/>
@@ -5018,23 +5018,23 @@
         </is>
       </c>
       <c r="C5" s="47">
-        <f>'Revenue Model'!C17</f>
+        <f>'Revenue Model'!C16</f>
         <v/>
       </c>
       <c r="D5" s="47">
-        <f>'Revenue Model'!D17</f>
+        <f>'Revenue Model'!D16</f>
         <v/>
       </c>
       <c r="E5" s="47">
-        <f>'Revenue Model'!E17</f>
+        <f>'Revenue Model'!E16</f>
         <v/>
       </c>
       <c r="F5" s="47">
-        <f>'Revenue Model'!F17</f>
+        <f>'Revenue Model'!F16</f>
         <v/>
       </c>
       <c r="G5" s="47">
-        <f>'Revenue Model'!G17</f>
+        <f>'Revenue Model'!G16</f>
         <v/>
       </c>
       <c r="H5" s="47">
@@ -5049,23 +5049,23 @@
         </is>
       </c>
       <c r="C6" s="16">
-        <f>'Operating Expenses'!E31</f>
+        <f>'Operating Expenses'!E17</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>'Operating Expenses'!F31</f>
+        <f>'Operating Expenses'!F17</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>'Operating Expenses'!G31</f>
+        <f>'Operating Expenses'!G17</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>'Operating Expenses'!H31</f>
+        <f>'Operating Expenses'!H17</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>'Operating Expenses'!I31</f>
+        <f>'Operating Expenses'!I17</f>
         <v/>
       </c>
       <c r="H6" s="16">
@@ -5134,23 +5134,23 @@
     <row r="9">
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Depreciation — existing plant (placeholder)</t>
-        </is>
-      </c>
-      <c r="C9" s="46" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="E9" s="46" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="F9" s="46" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="G9" s="46" t="n">
-        <v>2400000</v>
+          <t>Depreciation — existing plant (Q2-2026 actual)</t>
+        </is>
+      </c>
+      <c r="C9" s="62" t="n">
+        <v>362804</v>
+      </c>
+      <c r="D9" s="62" t="n">
+        <v>362804</v>
+      </c>
+      <c r="E9" s="62" t="n">
+        <v>362804</v>
+      </c>
+      <c r="F9" s="62" t="n">
+        <v>362804</v>
+      </c>
+      <c r="G9" s="62" t="n">
+        <v>362804</v>
       </c>
       <c r="H9" s="16">
         <f>SUM(C9:G9)</f>
@@ -5250,10 +5250,126 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Less: Interest expense (existing debt)</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="n">
+        <v>-465000</v>
+      </c>
+      <c r="D13" s="62" t="n">
+        <v>-455000</v>
+      </c>
+      <c r="E13" s="62" t="n">
+        <v>-445000</v>
+      </c>
+      <c r="F13" s="62" t="n">
+        <v>-435000</v>
+      </c>
+      <c r="G13" s="62" t="n">
+        <v>-425000</v>
+      </c>
+      <c r="H13" s="16">
+        <f>SUM(C13:G13)</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>Note: LLC pass-through; no entity income tax modeled (placeholder).</t>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Plus: Grant income (nonoperating)</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D14" s="62" t="n">
+        <v>850000</v>
+      </c>
+      <c r="E14" s="62" t="n">
+        <v>650000</v>
+      </c>
+      <c r="F14" s="62" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G14" s="62" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H14" s="16">
+        <f>SUM(C14:G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Plus: Other nonoperating income (net)</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D15" s="62" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E15" s="62" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F15" s="62" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G15" s="62" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H15" s="16">
+        <f>SUM(C15:G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="C16" s="47">
+        <f>C12+C13+C14+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="47">
+        <f>D12+D13+D14+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="47">
+        <f>E12+E13+E14+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="47">
+        <f>F12+F13+F14+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="47">
+        <f>G12+G13+G14+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="47">
+        <f>SUM(C16:G16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Nonoperating items anchored to Q2-2026 actuals; grant income is lumpy &amp; temporary. LLC pass-through; no entity income tax modeled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Note: GAAP net income is pressured by rising depreciation on the expanding $50M plant during the build — EBITDA is the operating-health metric.</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J17"/>
+  <dimension ref="B1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -5398,194 +5514,277 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Less: Cash interest (existing debt)</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="n">
+        <v>-465000</v>
+      </c>
+      <c r="D7" s="62" t="n">
+        <v>-455000</v>
+      </c>
+      <c r="E7" s="62" t="n">
+        <v>-445000</v>
+      </c>
+      <c r="F7" s="62" t="n">
+        <v>-435000</v>
+      </c>
+      <c r="G7" s="62" t="n">
+        <v>-425000</v>
+      </c>
+      <c r="H7" s="16">
+        <f>SUM(C7:G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Free cash flow before financing</t>
         </is>
       </c>
-      <c r="C7" s="47">
-        <f>C5+C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="47">
-        <f>D5+D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="47">
-        <f>E5+E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="47">
-        <f>F5+F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="47">
-        <f>G5+G6</f>
-        <v/>
-      </c>
-      <c r="H7" s="47">
-        <f>SUM(C7:G7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="41" t="inlineStr">
+      <c r="C8" s="47">
+        <f>C5+C6+C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="47">
+        <f>D5+D6+D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="47">
+        <f>E5+E6+E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="47">
+        <f>F5+F6+F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="47">
+        <f>G5+G6+G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="47">
+        <f>SUM(C8:G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Plus: Grant capital reimbursement</t>
+        </is>
+      </c>
+      <c r="C9" s="62" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D9" s="62" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E9" s="62" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F9" s="62" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G9" s="62" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H9" s="16">
+        <f>SUM(C9:G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Net cash need (after grant reimbursement)</t>
+        </is>
+      </c>
+      <c r="C10" s="47">
+        <f>C8+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="47">
+        <f>D8+D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="47">
+        <f>E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="47">
+        <f>F8+F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="47">
+        <f>G8+G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="47">
+        <f>SUM(C10:G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Cumulative cash requirement</t>
         </is>
       </c>
-      <c r="C8" s="59">
-        <f>C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="59">
-        <f>C8+D7</f>
-        <v/>
-      </c>
-      <c r="E8" s="59">
-        <f>D8+E7</f>
-        <v/>
-      </c>
-      <c r="F8" s="59">
-        <f>E8+F7</f>
-        <v/>
-      </c>
-      <c r="G8" s="59">
-        <f>F8+G7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="8" t="inlineStr">
+      <c r="C11" s="59">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="59">
+        <f>C11+D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="59">
+        <f>D11+E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="59">
+        <f>E11+F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="59">
+        <f>F11+G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Capital funding available</t>
         </is>
       </c>
-      <c r="C10" s="16">
+      <c r="C13" s="16">
         <f>'Capital Plan'!E23</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D13" s="16">
         <f>'Capital Plan'!F23</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E13" s="16">
         <f>'Capital Plan'!G23</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F13" s="16">
         <f>'Capital Plan'!H23</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G13" s="16">
         <f>'Capital Plan'!I23</f>
         <v/>
       </c>
-      <c r="H10" s="16">
-        <f>SUM(C10:G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="8" t="inlineStr">
+      <c r="H13" s="16">
+        <f>SUM(C13:G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Capital funding used</t>
         </is>
       </c>
-      <c r="C11" s="16">
+      <c r="C14" s="16">
         <f>'Capital Plan'!E24</f>
         <v/>
       </c>
-      <c r="D11" s="16">
+      <c r="D14" s="16">
         <f>'Capital Plan'!F24</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E14" s="16">
         <f>'Capital Plan'!G24</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F14" s="16">
         <f>'Capital Plan'!H24</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G14" s="16">
         <f>'Capital Plan'!I24</f>
         <v/>
       </c>
-      <c r="H11" s="16">
-        <f>SUM(C11:G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="41" t="inlineStr">
+      <c r="H14" s="16">
+        <f>SUM(C14:G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>Capital funding remaining</t>
         </is>
       </c>
-      <c r="C12" s="59">
+      <c r="C15" s="59">
         <f>'Capital Plan'!E25</f>
         <v/>
       </c>
-      <c r="D12" s="59">
+      <c r="D15" s="59">
         <f>'Capital Plan'!F25</f>
         <v/>
       </c>
-      <c r="E12" s="59">
+      <c r="E15" s="59">
         <f>'Capital Plan'!G25</f>
         <v/>
       </c>
-      <c r="F12" s="59">
+      <c r="F15" s="59">
         <f>'Capital Plan'!H25</f>
         <v/>
       </c>
-      <c r="G12" s="59">
+      <c r="G15" s="59">
         <f>'Capital Plan'!I25</f>
         <v/>
       </c>
-      <c r="H12" s="59">
-        <f>SUM(C12:G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="10" t="inlineStr">
+      <c r="H15" s="59">
+        <f>SUM(C15:G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>BREAK-EVEN ANALYSIS</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="31" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>EBITDA-positive from</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>2027 (Year 1)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="31" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>FCF-positive year (before financing)</t>
         </is>
       </c>
-      <c r="C16" s="68" t="inlineStr">
+      <c r="C19" s="68" t="inlineStr">
         <is>
           <t>Beyond plan horizon — sustained build capex</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="31" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Approx. EBITDA break-even subs (Yr-1 cost base)</t>
         </is>
       </c>
-      <c r="C17" s="68" t="inlineStr">
+      <c r="C20" s="68" t="inlineStr">
         <is>
           <t>See KPI tab</t>
         </is>
@@ -5841,23 +6040,23 @@
         </is>
       </c>
       <c r="D10" s="48">
-        <f>'Revenue Model'!C15/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2+('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2)/12</f>
+        <f>'Revenue Model'!C14/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2+('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2)/12</f>
         <v/>
       </c>
       <c r="E10" s="48">
-        <f>'Revenue Model'!D15/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2+('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2)/12</f>
+        <f>'Revenue Model'!D14/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2+('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2)/12</f>
         <v/>
       </c>
       <c r="F10" s="48">
-        <f>'Revenue Model'!E15/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2+('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2)/12</f>
+        <f>'Revenue Model'!E14/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2+('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2)/12</f>
         <v/>
       </c>
       <c r="G10" s="48">
-        <f>'Revenue Model'!F15/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2+('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2)/12</f>
+        <f>'Revenue Model'!F14/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2+('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2)/12</f>
         <v/>
       </c>
       <c r="H10" s="48">
-        <f>'Revenue Model'!G15/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2+('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2)/12</f>
+        <f>'Revenue Model'!G14/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2+('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2)/12</f>
         <v/>
       </c>
     </row>
@@ -5937,23 +6136,23 @@
         </is>
       </c>
       <c r="D13" s="18">
-        <f>'Revenue Model'!C17/((Assumptions!E25+SUM(Assumptions!E27:E27))+(Assumptions!E26+SUM(Assumptions!E28:E28)))</f>
+        <f>'Revenue Model'!C16/((Assumptions!E25+SUM(Assumptions!E27:E27))+(Assumptions!E26+SUM(Assumptions!E28:E28)))</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>'Revenue Model'!D17/((Assumptions!E25+SUM(Assumptions!E27:F27))+(Assumptions!E26+SUM(Assumptions!E28:F28)))</f>
+        <f>'Revenue Model'!D16/((Assumptions!E25+SUM(Assumptions!E27:F27))+(Assumptions!E26+SUM(Assumptions!E28:F28)))</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>'Revenue Model'!E17/((Assumptions!E25+SUM(Assumptions!E27:G27))+(Assumptions!E26+SUM(Assumptions!E28:G28)))</f>
+        <f>'Revenue Model'!E16/((Assumptions!E25+SUM(Assumptions!E27:G27))+(Assumptions!E26+SUM(Assumptions!E28:G28)))</f>
         <v/>
       </c>
       <c r="G13" s="18">
-        <f>'Revenue Model'!F17/((Assumptions!E25+SUM(Assumptions!E27:H27))+(Assumptions!E26+SUM(Assumptions!E28:H28)))</f>
+        <f>'Revenue Model'!F16/((Assumptions!E25+SUM(Assumptions!E27:H27))+(Assumptions!E26+SUM(Assumptions!E28:H28)))</f>
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>'Revenue Model'!G17/((Assumptions!E25+SUM(Assumptions!E27:I27))+(Assumptions!E26+SUM(Assumptions!E28:I28)))</f>
+        <f>'Revenue Model'!G16/((Assumptions!E25+SUM(Assumptions!E27:I27))+(Assumptions!E26+SUM(Assumptions!E28:I28)))</f>
         <v/>
       </c>
     </row>
@@ -6033,23 +6232,23 @@
         </is>
       </c>
       <c r="D16" s="18">
-        <f>('Operating Expenses'!E12+'Operating Expenses'!E13)/'Subscriber Forecast'!C51</f>
+        <f>('Operating Expenses'!E8+'Operating Expenses'!E9)/'Subscriber Forecast'!C51</f>
         <v/>
       </c>
       <c r="E16" s="18">
-        <f>('Operating Expenses'!F12+'Operating Expenses'!F13)/'Subscriber Forecast'!D51</f>
+        <f>('Operating Expenses'!F8+'Operating Expenses'!F9)/'Subscriber Forecast'!D51</f>
         <v/>
       </c>
       <c r="F16" s="18">
-        <f>('Operating Expenses'!G12+'Operating Expenses'!G13)/'Subscriber Forecast'!E51</f>
+        <f>('Operating Expenses'!G8+'Operating Expenses'!G9)/'Subscriber Forecast'!E51</f>
         <v/>
       </c>
       <c r="G16" s="18">
-        <f>('Operating Expenses'!H12+'Operating Expenses'!H13)/'Subscriber Forecast'!F51</f>
+        <f>('Operating Expenses'!H8+'Operating Expenses'!H9)/'Subscriber Forecast'!F51</f>
         <v/>
       </c>
       <c r="H16" s="18">
-        <f>('Operating Expenses'!I12+'Operating Expenses'!I13)/'Subscriber Forecast'!G51</f>
+        <f>('Operating Expenses'!I8+'Operating Expenses'!I9)/'Subscriber Forecast'!G51</f>
         <v/>
       </c>
     </row>
@@ -6119,23 +6318,23 @@
         </is>
       </c>
       <c r="D19" s="18">
-        <f>'Revenue Model'!C17/Assumptions!E41</f>
+        <f>'Revenue Model'!C16/Assumptions!E41</f>
         <v/>
       </c>
       <c r="E19" s="18">
-        <f>'Revenue Model'!D17/Assumptions!F41</f>
+        <f>'Revenue Model'!D16/Assumptions!F41</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>'Revenue Model'!E17/Assumptions!G41</f>
+        <f>'Revenue Model'!E16/Assumptions!G41</f>
         <v/>
       </c>
       <c r="G19" s="18">
-        <f>'Revenue Model'!F17/Assumptions!H41</f>
+        <f>'Revenue Model'!F16/Assumptions!H41</f>
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>'Revenue Model'!G17/Assumptions!I41</f>
+        <f>'Revenue Model'!G16/Assumptions!I41</f>
         <v/>
       </c>
     </row>
@@ -6355,23 +6554,23 @@
         </is>
       </c>
       <c r="D27" s="18">
-        <f>'Operating Expenses'!E31/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)</f>
+        <f>'Operating Expenses'!E17/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)</f>
         <v/>
       </c>
       <c r="E27" s="18">
-        <f>'Operating Expenses'!F31/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)</f>
+        <f>'Operating Expenses'!F17/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)</f>
         <v/>
       </c>
       <c r="F27" s="18">
-        <f>'Operating Expenses'!G31/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)</f>
+        <f>'Operating Expenses'!G17/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)</f>
         <v/>
       </c>
       <c r="G27" s="18">
-        <f>'Operating Expenses'!H31/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)</f>
+        <f>'Operating Expenses'!H17/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)</f>
         <v/>
       </c>
       <c r="H27" s="18">
-        <f>'Operating Expenses'!I31/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)</f>
+        <f>'Operating Expenses'!I17/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)</f>
         <v/>
       </c>
     </row>
@@ -6387,23 +6586,23 @@
         </is>
       </c>
       <c r="D28" s="19">
-        <f>'Income Statement'!C7/'Revenue Model'!C17</f>
+        <f>'Income Statement'!C7/'Revenue Model'!C16</f>
         <v/>
       </c>
       <c r="E28" s="19">
-        <f>'Income Statement'!D7/'Revenue Model'!D17</f>
+        <f>'Income Statement'!D7/'Revenue Model'!D16</f>
         <v/>
       </c>
       <c r="F28" s="19">
-        <f>'Income Statement'!E7/'Revenue Model'!E17</f>
+        <f>'Income Statement'!E7/'Revenue Model'!E16</f>
         <v/>
       </c>
       <c r="G28" s="19">
-        <f>'Income Statement'!F7/'Revenue Model'!F17</f>
+        <f>'Income Statement'!F7/'Revenue Model'!F16</f>
         <v/>
       </c>
       <c r="H28" s="19">
-        <f>'Income Statement'!G7/'Revenue Model'!G17</f>
+        <f>'Income Statement'!G7/'Revenue Model'!G16</f>
         <v/>
       </c>
     </row>
@@ -7814,7 +8013,7 @@
     </row>
     <row r="6">
       <c r="B6" s="11">
-        <f>'Revenue Model'!G17</f>
+        <f>'Revenue Model'!G16</f>
         <v/>
       </c>
       <c r="D6" s="11">
@@ -7822,7 +8021,7 @@
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>'Income Statement'!G7/'Revenue Model'!G17</f>
+        <f>'Income Statement'!G7/'Revenue Model'!G16</f>
         <v/>
       </c>
     </row>
@@ -7853,7 +8052,7 @@
         <v/>
       </c>
       <c r="F9" s="11">
-        <f>MIN('Cash Flow'!C8:G8)</f>
+        <f>MIN('Cash Flow'!C11:G11)</f>
         <v/>
       </c>
     </row>
@@ -7884,7 +8083,7 @@
         <v/>
       </c>
       <c r="F12" s="11">
-        <f>'Revenue Model'!H17</f>
+        <f>'Revenue Model'!H16</f>
         <v/>
       </c>
     </row>
@@ -7917,23 +8116,23 @@
         </is>
       </c>
       <c r="C17" s="16">
-        <f>'Revenue Model'!C17</f>
+        <f>'Revenue Model'!C16</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>'Revenue Model'!D17</f>
+        <f>'Revenue Model'!D16</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>'Revenue Model'!E17</f>
+        <f>'Revenue Model'!E16</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>'Revenue Model'!F17</f>
+        <f>'Revenue Model'!F16</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>'Revenue Model'!G17</f>
+        <f>'Revenue Model'!G16</f>
         <v/>
       </c>
     </row>
@@ -8052,23 +8251,23 @@
         </is>
       </c>
       <c r="C22" s="18">
-        <f>'Operating Expenses'!E31/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)</f>
+        <f>'Operating Expenses'!E17/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)</f>
         <v/>
       </c>
       <c r="D22" s="18">
-        <f>'Operating Expenses'!F31/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)</f>
+        <f>'Operating Expenses'!F17/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)</f>
         <v/>
       </c>
       <c r="E22" s="18">
-        <f>'Operating Expenses'!G31/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)</f>
+        <f>'Operating Expenses'!G17/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)</f>
         <v/>
       </c>
       <c r="F22" s="18">
-        <f>'Operating Expenses'!H31/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)</f>
+        <f>'Operating Expenses'!H17/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)</f>
         <v/>
       </c>
       <c r="G22" s="18">
-        <f>'Operating Expenses'!I31/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)</f>
+        <f>'Operating Expenses'!I17/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)</f>
         <v/>
       </c>
     </row>
@@ -8079,23 +8278,23 @@
         </is>
       </c>
       <c r="C23" s="19">
-        <f>'Income Statement'!C7/'Revenue Model'!C17</f>
+        <f>'Income Statement'!C7/'Revenue Model'!C16</f>
         <v/>
       </c>
       <c r="D23" s="19">
-        <f>'Income Statement'!D7/'Revenue Model'!D17</f>
+        <f>'Income Statement'!D7/'Revenue Model'!D16</f>
         <v/>
       </c>
       <c r="E23" s="19">
-        <f>'Income Statement'!E7/'Revenue Model'!E17</f>
+        <f>'Income Statement'!E7/'Revenue Model'!E16</f>
         <v/>
       </c>
       <c r="F23" s="19">
-        <f>'Income Statement'!F7/'Revenue Model'!F17</f>
+        <f>'Income Statement'!F7/'Revenue Model'!F16</f>
         <v/>
       </c>
       <c r="G23" s="19">
-        <f>'Income Statement'!G7/'Revenue Model'!G17</f>
+        <f>'Income Statement'!G7/'Revenue Model'!G16</f>
         <v/>
       </c>
     </row>
@@ -10427,49 +10626,49 @@
         </is>
       </c>
       <c r="D22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="L22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="M22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="N22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="P22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="Q22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="R22" s="35" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
@@ -10541,49 +10740,49 @@
         </is>
       </c>
       <c r="D24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="E24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="F24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="G24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="H24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="I24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="J24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="K24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="L24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="M24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="N24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="O24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="P24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="Q24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="R24" s="35" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25">
@@ -10655,49 +10854,49 @@
         </is>
       </c>
       <c r="D26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="E26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="F26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="G26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="H26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="I26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="J26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="K26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="L26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="M26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="N26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="O26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="P26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="Q26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
       <c r="R26" s="35" t="n">
-        <v>850</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27">
@@ -10769,49 +10968,49 @@
         </is>
       </c>
       <c r="D28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="N28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="P28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R28" s="35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -11396,19 +11595,19 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>0.35</v>
+        <v>0.012</v>
       </c>
       <c r="E39" s="34" t="n">
-        <v>0.35</v>
+        <v>0.012</v>
       </c>
       <c r="F39" s="34" t="n">
-        <v>0.35</v>
+        <v>0.012</v>
       </c>
       <c r="G39" s="34" t="n">
-        <v>0.35</v>
+        <v>0.012</v>
       </c>
       <c r="H39" s="34" t="n">
-        <v>0.35</v>
+        <v>0.012</v>
       </c>
       <c r="I39" s="34" t="n">
         <v>0.28</v>
@@ -11453,49 +11652,49 @@
         </is>
       </c>
       <c r="D40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R40" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -11510,19 +11709,19 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E41" s="34" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F41" s="34" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G41" s="34" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H41" s="34" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I41" s="34" t="n">
         <v>0.25</v>
@@ -11567,49 +11766,49 @@
         </is>
       </c>
       <c r="D42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R42" s="35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -13721,7 +13920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J19"/>
+  <dimension ref="B1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -13973,27 +14172,27 @@
     <row r="11">
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Equipment fees (ONT/router)</t>
+          <t>Residential other (equipment/misc)</t>
         </is>
       </c>
       <c r="C11" s="16">
-        <f>((('Subscriber Forecast'!C30+'Subscriber Forecast'!C33)/2)+(('Subscriber Forecast'!C35+'Subscriber Forecast'!C38)/2))*6*12</f>
+        <f>(('Subscriber Forecast'!C30+'Subscriber Forecast'!C33)/2)*2.9*12</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>((('Subscriber Forecast'!D30+'Subscriber Forecast'!D33)/2)+(('Subscriber Forecast'!D35+'Subscriber Forecast'!D38)/2))*6*12</f>
+        <f>(('Subscriber Forecast'!D30+'Subscriber Forecast'!D33)/2)*2.9*12</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>((('Subscriber Forecast'!E30+'Subscriber Forecast'!E33)/2)+(('Subscriber Forecast'!E35+'Subscriber Forecast'!E38)/2))*6*12</f>
+        <f>(('Subscriber Forecast'!E30+'Subscriber Forecast'!E33)/2)*2.9*12</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>((('Subscriber Forecast'!F30+'Subscriber Forecast'!F33)/2)+(('Subscriber Forecast'!F35+'Subscriber Forecast'!F38)/2))*6*12</f>
+        <f>(('Subscriber Forecast'!F30+'Subscriber Forecast'!F33)/2)*2.9*12</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>((('Subscriber Forecast'!G30+'Subscriber Forecast'!G33)/2)+(('Subscriber Forecast'!G35+'Subscriber Forecast'!G38)/2))*6*12</f>
+        <f>(('Subscriber Forecast'!G30+'Subscriber Forecast'!G33)/2)*2.9*12</f>
         <v/>
       </c>
       <c r="H11" s="16">
@@ -14004,23 +14203,23 @@
     <row r="12">
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Wholesale / dark fiber / IRU / transport</t>
+          <t>Dark fiber / IRU / transport (wholesale)</t>
         </is>
       </c>
       <c r="C12" s="46" t="n">
-        <v>180000</v>
+        <v>12000</v>
       </c>
       <c r="D12" s="46" t="n">
-        <v>240000</v>
+        <v>20000</v>
       </c>
       <c r="E12" s="46" t="n">
-        <v>320000</v>
+        <v>32000</v>
       </c>
       <c r="F12" s="46" t="n">
-        <v>410000</v>
+        <v>48000</v>
       </c>
       <c r="G12" s="46" t="n">
-        <v>500000</v>
+        <v>65000</v>
       </c>
       <c r="H12" s="16">
         <f>SUM(C12:G12)</f>
@@ -14030,23 +14229,23 @@
     <row r="13">
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Grant operating/admin revenue (if allowable)</t>
+          <t>Other telecom services</t>
         </is>
       </c>
       <c r="C13" s="46" t="n">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="D13" s="46" t="n">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="E13" s="46" t="n">
-        <v>70000</v>
+        <v>26000</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>70000</v>
+        <v>32000</v>
       </c>
       <c r="G13" s="46" t="n">
-        <v>60000</v>
+        <v>38000</v>
       </c>
       <c r="H13" s="16">
         <f>SUM(C13:G13)</f>
@@ -14054,148 +14253,122 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Other telecom services</t>
-        </is>
-      </c>
-      <c r="C14" s="46" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D14" s="46" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E14" s="46" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F14" s="46" t="n">
-        <v>85000</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <v>100000</v>
-      </c>
-      <c r="H14" s="16">
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>RECURRING REVENUE</t>
+        </is>
+      </c>
+      <c r="C14" s="47">
+        <f>C5+C6+C7+C8+C9+C10+C11+C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="47">
+        <f>D5+D6+D7+D8+D9+D10+D11+D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="47">
+        <f>E5+E6+E7+E8+E9+E10+E11+E12+E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="47">
+        <f>F5+F6+F7+F8+F9+F10+F11+F12+F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="47">
+        <f>G5+G6+G7+G8+G9+G10+G11+G12+G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="47">
         <f>SUM(C14:G14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>RECURRING REVENUE</t>
-        </is>
-      </c>
-      <c r="C15" s="47">
-        <f>C5+C6+C7+C8+C9+C10+C11+C12+C13+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="47">
-        <f>D5+D6+D7+D8+D9+D10+D11+D12+D13+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="47">
-        <f>E5+E6+E7+E8+E9+E10+E11+E12+E13+E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="47">
-        <f>F5+F6+F7+F8+F9+F10+F11+F12+F13+F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="47">
-        <f>G5+G6+G7+G8+G9+G10+G11+G12+G13+G14</f>
-        <v/>
-      </c>
-      <c r="H15" s="47">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Installation &amp; construction (nonrecurring)</t>
+        </is>
+      </c>
+      <c r="C15" s="16">
+        <f>'Subscriber Forecast'!C31*Assumptions!E38+'Subscriber Forecast'!C36*Assumptions!E39+'Subscriber Forecast'!C41*Assumptions!E40</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>'Subscriber Forecast'!D31*Assumptions!E38+'Subscriber Forecast'!D36*Assumptions!E39+'Subscriber Forecast'!D41*Assumptions!E40</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>'Subscriber Forecast'!E31*Assumptions!E38+'Subscriber Forecast'!E36*Assumptions!E39+'Subscriber Forecast'!E41*Assumptions!E40</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>'Subscriber Forecast'!F31*Assumptions!E38+'Subscriber Forecast'!F36*Assumptions!E39+'Subscriber Forecast'!F41*Assumptions!E40</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>'Subscriber Forecast'!G31*Assumptions!E38+'Subscriber Forecast'!G36*Assumptions!E39+'Subscriber Forecast'!G41*Assumptions!E40</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
         <f>SUM(C15:G15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Installation &amp; construction (nonrecurring)</t>
-        </is>
-      </c>
-      <c r="C16" s="16">
-        <f>'Subscriber Forecast'!C31*Assumptions!E38+'Subscriber Forecast'!C36*Assumptions!E39+'Subscriber Forecast'!C41*Assumptions!E40</f>
-        <v/>
-      </c>
-      <c r="D16" s="16">
-        <f>'Subscriber Forecast'!D31*Assumptions!E38+'Subscriber Forecast'!D36*Assumptions!E39+'Subscriber Forecast'!D41*Assumptions!E40</f>
-        <v/>
-      </c>
-      <c r="E16" s="16">
-        <f>'Subscriber Forecast'!E31*Assumptions!E38+'Subscriber Forecast'!E36*Assumptions!E39+'Subscriber Forecast'!E41*Assumptions!E40</f>
-        <v/>
-      </c>
-      <c r="F16" s="16">
-        <f>'Subscriber Forecast'!F31*Assumptions!E38+'Subscriber Forecast'!F36*Assumptions!E39+'Subscriber Forecast'!F41*Assumptions!E40</f>
-        <v/>
-      </c>
-      <c r="G16" s="16">
-        <f>'Subscriber Forecast'!G31*Assumptions!E38+'Subscriber Forecast'!G36*Assumptions!E39+'Subscriber Forecast'!G41*Assumptions!E40</f>
-        <v/>
-      </c>
-      <c r="H16" s="16">
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="C16" s="47">
+        <f>C14+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="47">
+        <f>D14+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="47">
+        <f>E14+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="47">
+        <f>F14+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="47">
+        <f>G14+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="47">
         <f>SUM(C16:G16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>TOTAL REVENUE</t>
-        </is>
-      </c>
-      <c r="C17" s="47">
-        <f>C15+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="47">
-        <f>D15+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="47">
-        <f>E15+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="47">
-        <f>F15+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="47">
-        <f>G15+G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="47">
-        <f>SUM(C17:G17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="31" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Blended ARPU (recurring/sub/mo)</t>
         </is>
       </c>
-      <c r="C19" s="48">
-        <f>C15/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2+('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2)/12</f>
-        <v/>
-      </c>
-      <c r="D19" s="48">
-        <f>D15/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2+('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2)/12</f>
-        <v/>
-      </c>
-      <c r="E19" s="48">
-        <f>E15/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2+('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2)/12</f>
-        <v/>
-      </c>
-      <c r="F19" s="48">
-        <f>F15/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2+('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2)/12</f>
-        <v/>
-      </c>
-      <c r="G19" s="48">
-        <f>G15/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2+('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2)/12</f>
+      <c r="C18" s="48">
+        <f>C14/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2+('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2)/12</f>
+        <v/>
+      </c>
+      <c r="D18" s="48">
+        <f>D14/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2+('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2)/12</f>
+        <v/>
+      </c>
+      <c r="E18" s="48">
+        <f>E14/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2+('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2)/12</f>
+        <v/>
+      </c>
+      <c r="F18" s="48">
+        <f>F14/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2+('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2)/12</f>
+        <v/>
+      </c>
+      <c r="G18" s="48">
+        <f>G14/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2+('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2)/12</f>
         <v/>
       </c>
     </row>
@@ -14214,7 +14387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J40"/>
+  <dimension ref="B1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="2" max="2"/>
@@ -14286,7 +14459,7 @@
     <row r="5">
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Internet transit / bandwidth</t>
+          <t>Cost of goods sold (transit / network direct)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -14300,35 +14473,35 @@
         </is>
       </c>
       <c r="E5" s="16">
-        <f>((('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)*2.5*12*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(642492*(((('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)+(('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2))/5188)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>((('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)*2.5*12*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(642492*(((('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)+(('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2))/5188)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>((('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)*2.5*12*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(642492*(((('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)+(('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2))/5188)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>((('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)*2.5*12*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(642492*(((('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)+(('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2))/5188)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>((('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)*2.5*12*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(642492*(((('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)+(('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2))/5188)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Fiber leases &amp; transport</t>
+          <t>LREMC intercompany allocation</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -14337,183 +14510,183 @@
         </is>
       </c>
       <c r="E6" s="16">
-        <f>((180000+12000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(380552*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>((180000+12000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(380552*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>((180000+12000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(380552*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>((180000+12000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(380552*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>((180000+12000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(380552*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Pole attachment expense</t>
+          <t>Engineering &amp; operations</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>NetOps</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Semi-var</t>
         </is>
       </c>
       <c r="E7" s="16">
-        <f>(((Assumptions!E25+SUM(Assumptions!E27:E27))+(Assumptions!E26+SUM(Assumptions!E28:E28)))*0.55*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(864540*(0.5+0.5*(((('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)+(('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2))/5188))*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>(((Assumptions!E25+SUM(Assumptions!E27:F27))+(Assumptions!E26+SUM(Assumptions!E28:F28)))*0.55*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(864540*(0.5+0.5*(((('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)+(('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2))/5188))*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>(((Assumptions!E25+SUM(Assumptions!E27:G27))+(Assumptions!E26+SUM(Assumptions!E28:G28)))*0.55*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(864540*(0.5+0.5*(((('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)+(('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2))/5188))*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>(((Assumptions!E25+SUM(Assumptions!E27:H27))+(Assumptions!E26+SUM(Assumptions!E28:H28)))*0.55*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(864540*(0.5+0.5*(((('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)+(('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2))/5188))*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>(((Assumptions!E25+SUM(Assumptions!E27:I27))+(Assumptions!E26+SUM(Assumptions!E28:I28)))*0.55*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(864540*(0.5+0.5*(((('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)+(('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2))/5188))*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Fiber maintenance</t>
+          <t>Marketing &amp; advertising</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>S&amp;M</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Semi-var</t>
         </is>
       </c>
       <c r="E8" s="16">
-        <f>((95000+15000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(318412*(0.4+0.6*(((('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)+(('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2))/5188))*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>((95000+15000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(318412*(0.4+0.6*(((('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)+(('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2))/5188))*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>((95000+15000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(318412*(0.4+0.6*(((('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)+(('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2))/5188))*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>((95000+15000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(318412*(0.4+0.6*(((('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)+(('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2))/5188))*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>((95000+15000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(318412*(0.4+0.6*(((('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)+(('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2))/5188))*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Network monitoring / NOC</t>
+          <t>Sales &amp; customer support</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>S&amp;M</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Semi-var</t>
         </is>
       </c>
       <c r="E9" s="16">
-        <f>((140000+10000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(233336*(0.3+0.7*(((('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)+(('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2))/5188))*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>((140000+10000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(233336*(0.3+0.7*(((('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)+(('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2))/5188))*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>((140000+10000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(233336*(0.3+0.7*(((('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)+(('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2))/5188))*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>((140000+10000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(233336*(0.3+0.7*(((('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)+(('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2))/5188))*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>((140000+10000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(233336*(0.3+0.7*(((('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)+(('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2))/5188))*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Voice platform</t>
+          <t>General &amp; administrative</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Semi-var</t>
         </is>
       </c>
       <c r="E10" s="16">
-        <f>((('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2)*8*12*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(1496052*(0.55+0.45*(Assumptions!E41/18))*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>((('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2)*8*12*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(1496052*(0.55+0.45*(Assumptions!F41/18))*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>((('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2)*8*12*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(1496052*(0.55+0.45*(Assumptions!G41/18))*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>((('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2)*8*12*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(1496052*(0.55+0.45*(Assumptions!H41/18))*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>((('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2)*8*12*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(1496052*(0.55+0.45*(Assumptions!I41/18))*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Emergency restoration</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -14522,912 +14695,394 @@
         </is>
       </c>
       <c r="E11" s="16">
-        <f>(75000*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(124314*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>(75000*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(124314*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>(75000*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(124314*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>(75000*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(124314*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>(75000*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(124314*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Marketing &amp; advertising</t>
+          <t>Human resources</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>S&amp;M</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>Semi-var</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E12" s="16">
-        <f>('Subscriber Forecast'!C51*Assumptions!E31+120000*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>(158562*(0.4+0.6*(Assumptions!E41/18))*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>('Subscriber Forecast'!D51*Assumptions!E31+120000*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>(158562*(0.4+0.6*(Assumptions!F41/18))*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>('Subscriber Forecast'!E51*Assumptions!E31+120000*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>(158562*(0.4+0.6*(Assumptions!G41/18))*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>('Subscriber Forecast'!F51*Assumptions!E31+120000*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>(158562*(0.4+0.6*(Assumptions!H41/18))*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>('Subscriber Forecast'!G51*Assumptions!E31+120000*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>(158562*(0.4+0.6*(Assumptions!I41/18))*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Sales commissions</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>S&amp;M</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E13" s="16">
-        <f>('Revenue Model'!C15*0.015)*Assumptions!E33</f>
+        <f>(39042*(0.5+0.5*(((('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)+(('Subscriber Forecast'!C45+'Subscriber Forecast'!C48)/2))/5188))*(1+Assumptions!E32)^1)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>('Revenue Model'!D15*0.015)*Assumptions!E33</f>
+        <f>(39042*(0.5+0.5*(((('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)+(('Subscriber Forecast'!D45+'Subscriber Forecast'!D48)/2))/5188))*(1+Assumptions!E32)^2)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>('Revenue Model'!E15*0.015)*Assumptions!E33</f>
+        <f>(39042*(0.5+0.5*(((('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)+(('Subscriber Forecast'!E45+'Subscriber Forecast'!E48)/2))/5188))*(1+Assumptions!E32)^3)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>('Revenue Model'!F15*0.015)*Assumptions!E33</f>
+        <f>(39042*(0.5+0.5*(((('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)+(('Subscriber Forecast'!F45+'Subscriber Forecast'!F48)/2))/5188))*(1+Assumptions!E32)^4)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>('Revenue Model'!G15*0.015)*Assumptions!E33</f>
+        <f>(39042*(0.5+0.5*(((('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)+(('Subscriber Forecast'!G45+'Subscriber Forecast'!G48)/2))/5188))*(1+Assumptions!E32)^5)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Vehicle fleet (fuel/repairs/ins/lease)</t>
+          <t>Taxes &amp; regulatory fees</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>NetOps</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>Semi-var</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="E14" s="16">
-        <f>(9500*MAX(8,ROUND(Assumptions!E41*0.55,0))*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>('Revenue Model'!C14*0.0034)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>(9500*MAX(8,ROUND(Assumptions!F41*0.55,0))*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>('Revenue Model'!D14*0.0034)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>(9500*MAX(8,ROUND(Assumptions!G41*0.55,0))*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>('Revenue Model'!E14*0.0034)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>(9500*MAX(8,ROUND(Assumptions!H41*0.55,0))*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>('Revenue Model'!F14*0.0034)*Assumptions!E33</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>(9500*MAX(8,ROUND(Assumptions!I41*0.55,0))*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>('Revenue Model'!G14*0.0034)*Assumptions!E33</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Tools, test &amp; safety equipment</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>NetOps</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E15" s="16">
-        <f>((45000+4000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>((45000+4000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G15" s="16">
-        <f>((45000+4000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H15" s="16">
-        <f>((45000+4000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I15" s="16">
-        <f>((45000+4000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>Subtotal (pre-contingency)</t>
+        </is>
+      </c>
+      <c r="E15" s="49">
+        <f>SUM(E5:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="49">
+        <f>SUM(F5:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="49">
+        <f>SUM(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="49">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="49">
+        <f>SUM(I5:I14)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Warehouse &amp; inventory</t>
+          <t>Contingency</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>NetOps</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Semi-var</t>
         </is>
       </c>
       <c r="E16" s="16">
-        <f>((60000+5000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>E15*0.02</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>((60000+5000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>F15*0.02</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>((60000+5000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>G15*0.02</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>((60000+5000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>H15*0.02</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>((60000+5000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>I15*0.02</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Contractor labor</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>NetOps</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>Semi-var</t>
-        </is>
-      </c>
-      <c r="E17" s="16">
-        <f>((650000+60000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f>((650000+60000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G17" s="16">
-        <f>((650000+60000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H17" s="16">
-        <f>((650000+60000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I17" s="16">
-        <f>((650000+60000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Salaries, OT, benefits (fully loaded)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E18" s="16">
-        <f>'Fully Loaded Labor Cost'!C32</f>
-        <v/>
-      </c>
-      <c r="F18" s="16">
-        <f>'Fully Loaded Labor Cost'!D32</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <f>'Fully Loaded Labor Cost'!E32</f>
-        <v/>
-      </c>
-      <c r="H18" s="16">
-        <f>'Fully Loaded Labor Cost'!F32</f>
-        <v/>
-      </c>
-      <c r="I18" s="16">
-        <f>'Fully Loaded Labor Cost'!G32</f>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSE</t>
+        </is>
+      </c>
+      <c r="E17" s="47">
+        <f>E15+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="47">
+        <f>F15+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="47">
+        <f>G15+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="47">
+        <f>H15+H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="47">
+        <f>I15+I16</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Software / OSS / BSS / CRM / GIS / billing</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E19" s="16">
-        <f>((260000+20000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F19" s="16">
-        <f>((260000+20000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G19" s="16">
-        <f>((260000+20000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H19" s="16">
-        <f>((260000+20000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I19" s="16">
-        <f>((260000+20000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
-        <v/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>By classification:</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Billing &amp; payment processing fees</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>Variable</t>
+          <t xml:space="preserve">  Direct cost of service</t>
         </is>
       </c>
       <c r="E20" s="16">
-        <f>('Revenue Model'!C15*0.02)*Assumptions!E33</f>
+        <f>E5</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>('Revenue Model'!D15*0.02)*Assumptions!E33</f>
+        <f>F5</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>('Revenue Model'!E15*0.02)*Assumptions!E33</f>
+        <f>G5</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>('Revenue Model'!F15*0.02)*Assumptions!E33</f>
+        <f>H5</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>('Revenue Model'!G15*0.02)*Assumptions!E33</f>
+        <f>I5</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Customer support</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>Semi-var</t>
+          <t xml:space="preserve">  Sales &amp; marketing</t>
         </is>
       </c>
       <c r="E21" s="16">
-        <f>((110000+25000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>E8+E9</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>((110000+25000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>F8+F9</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>((110000+25000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>G8+G9</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>((110000+25000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>H8+H9</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>((110000+25000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>I8+I9</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Property &amp; casualty insurance</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t xml:space="preserve">  Network operations</t>
         </is>
       </c>
       <c r="E22" s="16">
-        <f>((185000+10000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>E7</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>((185000+10000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>F7</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>((185000+10000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>G7</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>((185000+10000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>H7</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>((185000+10000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>I7</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Professional / legal / consulting / regulatory</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t xml:space="preserve">  General &amp; administrative</t>
         </is>
       </c>
       <c r="E23" s="16">
-        <f>((210000+12000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
+        <f>E6+E10+E11+E12+E13+E14+E16</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>((210000+12000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
+        <f>F6+F10+F11+F12+F13+F14+F16</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>((210000+12000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
+        <f>G6+G10+G11+G12+G13+G14+G16</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>((210000+12000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
+        <f>H6+H10+H11+H12+H13+H14+H16</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>((210000+12000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Training &amp; travel</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>Semi-var</t>
-        </is>
-      </c>
-      <c r="E24" s="16">
-        <f>((65000+6000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F24" s="16">
-        <f>((65000+6000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G24" s="16">
-        <f>((65000+6000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H24" s="16">
-        <f>((65000+6000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I24" s="16">
-        <f>((65000+6000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+        <f>I6+I10+I11+I12+I13+I14+I16</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Office &amp; administrative</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E25" s="16">
-        <f>((140000+12000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F25" s="16">
-        <f>((140000+12000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G25" s="16">
-        <f>((140000+12000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H25" s="16">
-        <f>((140000+12000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I25" s="16">
-        <f>((140000+12000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>OpEx per subscriber ($/yr)</t>
+        </is>
+      </c>
+      <c r="E25" s="18">
+        <f>'Operating Expenses'!E17/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)</f>
+        <v/>
+      </c>
+      <c r="F25" s="18">
+        <f>'Operating Expenses'!F17/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)</f>
+        <v/>
+      </c>
+      <c r="G25" s="18">
+        <f>'Operating Expenses'!G17/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)</f>
+        <v/>
+      </c>
+      <c r="H25" s="18">
+        <f>'Operating Expenses'!H17/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)</f>
+        <v/>
+      </c>
+      <c r="I25" s="18">
+        <f>'Operating Expenses'!I17/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E26" s="16">
-        <f>((70000+6000*0)*(1+Assumptions!E32)^0)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F26" s="16">
-        <f>((70000+6000*1)*(1+Assumptions!E32)^1)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G26" s="16">
-        <f>((70000+6000*2)*(1+Assumptions!E32)^2)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H26" s="16">
-        <f>((70000+6000*3)*(1+Assumptions!E32)^3)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I26" s="16">
-        <f>((70000+6000*4)*(1+Assumptions!E32)^4)*Assumptions!E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Bad debt</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="E27" s="16">
-        <f>('Revenue Model'!C17*0.008)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F27" s="16">
-        <f>('Revenue Model'!D17*0.008)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G27" s="16">
-        <f>('Revenue Model'!E17*0.008)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H27" s="16">
-        <f>('Revenue Model'!F17*0.008)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I27" s="16">
-        <f>('Revenue Model'!G17*0.008)*Assumptions!E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Taxes &amp; regulatory fees (USF etc.)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="E28" s="16">
-        <f>('Revenue Model'!C15*0.015)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="F28" s="16">
-        <f>('Revenue Model'!D15*0.015)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="G28" s="16">
-        <f>('Revenue Model'!E15*0.015)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="H28" s="16">
-        <f>('Revenue Model'!F15*0.015)*Assumptions!E33</f>
-        <v/>
-      </c>
-      <c r="I28" s="16">
-        <f>('Revenue Model'!G15*0.015)*Assumptions!E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="38" t="inlineStr">
-        <is>
-          <t>Subtotal (pre-contingency)</t>
-        </is>
-      </c>
-      <c r="E29" s="49">
-        <f>SUM(E5:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="49">
-        <f>SUM(F5:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="49">
-        <f>SUM(G5:G28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="49">
-        <f>SUM(H5:H28)</f>
-        <v/>
-      </c>
-      <c r="I29" s="49">
-        <f>SUM(I5:I28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Contingency</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Semi-var</t>
-        </is>
-      </c>
-      <c r="E30" s="16">
-        <f>E29*0.015</f>
-        <v/>
-      </c>
-      <c r="F30" s="16">
-        <f>F29*0.015</f>
-        <v/>
-      </c>
-      <c r="G30" s="16">
-        <f>G29*0.015</f>
-        <v/>
-      </c>
-      <c r="H30" s="16">
-        <f>H29*0.015</f>
-        <v/>
-      </c>
-      <c r="I30" s="16">
-        <f>I29*0.015</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="43" t="inlineStr">
-        <is>
-          <t>TOTAL OPERATING EXPENSE</t>
-        </is>
-      </c>
-      <c r="E31" s="47">
-        <f>E29+E30</f>
-        <v/>
-      </c>
-      <c r="F31" s="47">
-        <f>F29+F30</f>
-        <v/>
-      </c>
-      <c r="G31" s="47">
-        <f>G29+G30</f>
-        <v/>
-      </c>
-      <c r="H31" s="47">
-        <f>H29+H30</f>
-        <v/>
-      </c>
-      <c r="I31" s="47">
-        <f>I29+I30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>By classification:</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Direct cost of service</t>
-        </is>
-      </c>
-      <c r="E34" s="16">
-        <f>E5+E6+E7+E8+E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F34" s="16">
-        <f>F5+F6+F7+F8+F9+F10+F11</f>
-        <v/>
-      </c>
-      <c r="G34" s="16">
-        <f>G5+G6+G7+G8+G9+G10+G11</f>
-        <v/>
-      </c>
-      <c r="H34" s="16">
-        <f>H5+H6+H7+H8+H9+H10+H11</f>
-        <v/>
-      </c>
-      <c r="I34" s="16">
-        <f>I5+I6+I7+I8+I9+I10+I11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales &amp; marketing</t>
-        </is>
-      </c>
-      <c r="E35" s="16">
-        <f>E12+E13</f>
-        <v/>
-      </c>
-      <c r="F35" s="16">
-        <f>F12+F13</f>
-        <v/>
-      </c>
-      <c r="G35" s="16">
-        <f>G12+G13</f>
-        <v/>
-      </c>
-      <c r="H35" s="16">
-        <f>H12+H13</f>
-        <v/>
-      </c>
-      <c r="I35" s="16">
-        <f>I12+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Network operations</t>
-        </is>
-      </c>
-      <c r="E36" s="16">
-        <f>E14+E15+E16+E17</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>F14+F15+F16+F17</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>G14+G15+G16+G17</f>
-        <v/>
-      </c>
-      <c r="H36" s="16">
-        <f>H14+H15+H16+H17</f>
-        <v/>
-      </c>
-      <c r="I36" s="16">
-        <f>I14+I15+I16+I17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  General &amp; administrative</t>
-        </is>
-      </c>
-      <c r="E37" s="16">
-        <f>E18+E19+E20+E21+E22+E23+E24+E25+E26+E27+E28+E30</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f>F18+F19+F20+F21+F22+F23+F24+F25+F26+F27+F28+F30</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f>G18+G19+G20+G21+G22+G23+G24+G25+G26+G27+G28+G30</f>
-        <v/>
-      </c>
-      <c r="H37" s="16">
-        <f>H18+H19+H20+H21+H22+H23+H24+H25+H26+H27+H28+H30</f>
-        <v/>
-      </c>
-      <c r="I37" s="16">
-        <f>I18+I19+I20+I21+I22+I23+I24+I25+I26+I27+I28+I30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="31" t="inlineStr">
-        <is>
-          <t>OpEx per subscriber ($/yr)</t>
-        </is>
-      </c>
-      <c r="E39" s="18">
-        <f>'Operating Expenses'!E31/(('Subscriber Forecast'!C50+'Subscriber Forecast'!C49)/2)</f>
-        <v/>
-      </c>
-      <c r="F39" s="18">
-        <f>'Operating Expenses'!F31/(('Subscriber Forecast'!D50+'Subscriber Forecast'!D49)/2)</f>
-        <v/>
-      </c>
-      <c r="G39" s="18">
-        <f>'Operating Expenses'!G31/(('Subscriber Forecast'!E50+'Subscriber Forecast'!E49)/2)</f>
-        <v/>
-      </c>
-      <c r="H39" s="18">
-        <f>'Operating Expenses'!H31/(('Subscriber Forecast'!F50+'Subscriber Forecast'!F49)/2)</f>
-        <v/>
-      </c>
-      <c r="I39" s="18">
-        <f>'Operating Expenses'!I31/(('Subscriber Forecast'!G50+'Subscriber Forecast'!G49)/2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="31" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>OpEx per revenue dollar</t>
         </is>
       </c>
-      <c r="E40" s="50">
-        <f>'Operating Expenses'!E31/'Revenue Model'!C17</f>
-        <v/>
-      </c>
-      <c r="F40" s="50">
-        <f>'Operating Expenses'!F31/'Revenue Model'!D17</f>
-        <v/>
-      </c>
-      <c r="G40" s="50">
-        <f>'Operating Expenses'!G31/'Revenue Model'!E17</f>
-        <v/>
-      </c>
-      <c r="H40" s="50">
-        <f>'Operating Expenses'!H31/'Revenue Model'!F17</f>
-        <v/>
-      </c>
-      <c r="I40" s="50">
-        <f>'Operating Expenses'!I31/'Revenue Model'!G17</f>
+      <c r="E26" s="50">
+        <f>'Operating Expenses'!E17/'Revenue Model'!C16</f>
+        <v/>
+      </c>
+      <c r="F26" s="50">
+        <f>'Operating Expenses'!F17/'Revenue Model'!D16</f>
+        <v/>
+      </c>
+      <c r="G26" s="50">
+        <f>'Operating Expenses'!G17/'Revenue Model'!E16</f>
+        <v/>
+      </c>
+      <c r="H26" s="50">
+        <f>'Operating Expenses'!H17/'Revenue Model'!F16</f>
+        <v/>
+      </c>
+      <c r="I26" s="50">
+        <f>'Operating Expenses'!I17/'Revenue Model'!G16</f>
         <v/>
       </c>
     </row>
